--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,14 +848,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45183.57416598625</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -901,26 +897,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
@@ -952,7 +928,7 @@
       </c>
       <c r="C33" s="30" t="n"/>
       <c r="D33" s="14" t="n">
-        <v>2271.585</v>
+        <v>2498.744</v>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" s="1">
@@ -968,7 +944,7 @@
       </c>
       <c r="C34" s="30" t="n"/>
       <c r="D34" s="14" t="n">
-        <v>2271.585</v>
+        <v>2498.744</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="1">
@@ -984,7 +960,7 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="14" t="n">
-        <v>2971.608</v>
+        <v>3268.769</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="1">
@@ -1000,7 +976,7 @@
       </c>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="14" t="n">
-        <v>2971.631</v>
+        <v>3268.794</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="1">
@@ -1016,7 +992,7 @@
       </c>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="14" t="n">
-        <v>2971.608</v>
+        <v>3268.769</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="1">
@@ -1032,14 +1008,9 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="14" t="n">
-        <v>3745.792</v>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
+        <v>4120.371</v>
+      </c>
+    </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
@@ -1047,7 +1018,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="11" t="n"/>
     </row>
@@ -1061,16 +1031,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,7 +848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,7 +848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,7 +848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,7 +848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,10 +848,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45267</v>
+        <v>45264.54809164778</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -897,6 +901,26 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
@@ -928,7 +952,7 @@
       </c>
       <c r="C33" s="30" t="n"/>
       <c r="D33" s="14" t="n">
-        <v>2498.744</v>
+        <v>3324.72</v>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" s="1">
@@ -944,7 +968,7 @@
       </c>
       <c r="C34" s="30" t="n"/>
       <c r="D34" s="14" t="n">
-        <v>2498.744</v>
+        <v>3324.72</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="1">
@@ -960,7 +984,7 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="14" t="n">
-        <v>3268.769</v>
+        <v>4349.29</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="1">
@@ -976,7 +1000,7 @@
       </c>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="14" t="n">
-        <v>3268.794</v>
+        <v>4349.32</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="1">
@@ -992,7 +1016,7 @@
       </c>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="14" t="n">
-        <v>3268.769</v>
+        <v>4349.29</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="1">
@@ -1008,9 +1032,14 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="14" t="n">
-        <v>4120.371</v>
-      </c>
-    </row>
+        <v>5482.4</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
@@ -1018,6 +1047,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="11" t="n"/>
     </row>
@@ -1031,16 +1061,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,14 +848,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45264.54809164778</v>
+        <v>45273</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -901,26 +897,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
@@ -952,7 +928,7 @@
       </c>
       <c r="C33" s="30" t="n"/>
       <c r="D33" s="14" t="n">
-        <v>3324.72</v>
+        <v>4022.91</v>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" s="1">
@@ -968,7 +944,7 @@
       </c>
       <c r="C34" s="30" t="n"/>
       <c r="D34" s="14" t="n">
-        <v>3324.72</v>
+        <v>4022.91</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="1">
@@ -984,7 +960,7 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="14" t="n">
-        <v>4349.29</v>
+        <v>5262.64</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="1">
@@ -1000,7 +976,7 @@
       </c>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="14" t="n">
-        <v>4349.32</v>
+        <v>5262.68</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="1">
@@ -1016,7 +992,7 @@
       </c>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="14" t="n">
-        <v>4349.29</v>
+        <v>5262.64</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="1">
@@ -1032,14 +1008,9 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="14" t="n">
-        <v>5482.4</v>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
+        <v>6633.7</v>
+      </c>
+    </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
@@ -1047,7 +1018,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="11" t="n"/>
     </row>
@@ -1061,16 +1031,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,7 +848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45273</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="C33" s="30" t="n"/>
       <c r="D33" s="14" t="n">
-        <v>4022.91</v>
+        <v>2498.744</v>
       </c>
     </row>
     <row r="34" ht="17.25" customHeight="1" s="1">
@@ -944,7 +944,7 @@
       </c>
       <c r="C34" s="30" t="n"/>
       <c r="D34" s="14" t="n">
-        <v>4022.91</v>
+        <v>2498.744</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="1">
@@ -960,7 +960,7 @@
       </c>
       <c r="C35" s="28" t="n"/>
       <c r="D35" s="14" t="n">
-        <v>5262.64</v>
+        <v>3268.769</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="1">
@@ -976,7 +976,7 @@
       </c>
       <c r="C36" s="28" t="n"/>
       <c r="D36" s="14" t="n">
-        <v>5262.68</v>
+        <v>3268.794</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="1">
@@ -992,7 +992,7 @@
       </c>
       <c r="C37" s="28" t="n"/>
       <c r="D37" s="14" t="n">
-        <v>5262.64</v>
+        <v>3268.769</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="1">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="14" t="n">
-        <v>6633.7</v>
+        <v>4120.371</v>
       </c>
     </row>
     <row r="44">
@@ -1030,17 +1030,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/PITONES ROSCA W..xlsx
+++ b/LISTAS/ma/PITONES ROSCA W..xlsx
@@ -848,7 +848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="23" t="n">
-        <v>45286</v>
+        <v>45287</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
